--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -3607,7 +3607,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -7261,7 +7261,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="7">
                 <v>0</v>
@@ -8881,13 +8881,13 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="7">
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -10249,7 +10249,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -10897,7 +10897,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -13306,7 +13306,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="4" t="n">
         <v>0</v>
@@ -13340,13 +13340,13 @@
         <v>0</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -13390,7 +13390,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>2</v>
@@ -14154,7 +14154,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -15209,7 +15209,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>1</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -610,7 +610,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -3430,7 +3430,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -6361,7 +6361,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -10909,7 +10909,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -13402,7 +13402,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -13601,7 +13601,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>0</v>
@@ -14114,7 +14114,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
@@ -14594,7 +14594,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>0</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -1783,7 +1783,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -3106,7 +3106,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -3430,7 +3430,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -3491,7 +3491,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5002,10 +5002,10 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -5308,7 +5308,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -7984,7 +7984,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -8560,7 +8560,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -8704,7 +8704,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -11089,7 +11089,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -13436,7 +13436,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -13794,7 +13794,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -14064,7 +14064,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
@@ -14114,7 +14114,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
@@ -14385,10 +14385,10 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
@@ -14429,7 +14429,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0</v>
@@ -14887,7 +14887,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -4555,7 +4555,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -4702,7 +4702,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -5302,10 +5302,10 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -5617,7 +5617,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -7261,7 +7261,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="7">
                 <v>0</v>
@@ -7987,7 +7987,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -8563,7 +8563,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -10921,7 +10921,7 @@
                 <v>1</v>
               </pt>
               <pt idx="8">
-                <v>2</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -13254,7 +13254,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>0</v>
@@ -13306,7 +13306,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" s="4" t="n">
         <v>0</v>
@@ -13414,7 +13414,7 @@
         <v>1</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -14331,7 +14331,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>0</v>
@@ -14423,10 +14423,10 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>1</v>
@@ -14826,7 +14826,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -14890,7 +14890,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -2944,7 +2944,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -3430,7 +3430,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -3491,7 +3491,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6364,7 +6364,7 @@
                 <v>1</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6505,7 +6505,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -6937,7 +6937,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -7408,7 +7408,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -7981,7 +7981,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -14039,7 +14039,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>0</v>
@@ -14114,7 +14114,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
@@ -14597,7 +14597,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>0</v>
@@ -14693,7 +14693,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0</v>
@@ -14820,7 +14820,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>1</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -265,7 +265,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="7">
                 <v>0</v>
@@ -2461,7 +2461,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -2470,7 +2470,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -3109,7 +3109,7 @@
                 <v>1</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -3268,10 +3268,10 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -3280,7 +3280,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -4702,7 +4702,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -5002,7 +5002,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -7261,7 +7261,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="7">
                 <v>0</v>
@@ -8881,7 +8881,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="7">
                 <v>0</v>
@@ -10903,7 +10903,7 @@
                 <v>2</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -13170,7 +13170,7 @@
         <v>0</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" s="4" t="n">
         <v>0</v>
@@ -13306,7 +13306,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" s="4" t="n">
         <v>0</v>
@@ -13340,7 +13340,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>0</v>
@@ -13396,7 +13396,7 @@
         <v>2</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -13967,7 +13967,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>0</v>
@@ -14067,7 +14067,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>0</v>
@@ -14089,10 +14089,10 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
@@ -14101,7 +14101,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>0</v>
@@ -14385,7 +14385,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>1</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -4702,7 +4702,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -4757,7 +4757,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5005,7 +5005,7 @@
                 <v>2</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -5302,7 +5302,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -6652,7 +6652,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6793,7 +6793,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -6937,7 +6937,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>1</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -10249,13 +10249,13 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -10301,7 +10301,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -10897,13 +10897,13 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -10921,7 +10921,7 @@
                 <v>1</v>
               </pt>
               <pt idx="8">
-                <v>3</v>
+                <v>5</v>
               </pt>
             </numLit>
           </val>
@@ -10967,7 +10967,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -13390,13 +13390,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -13414,7 +13414,7 @@
         <v>1</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>0</v>
@@ -14388,7 +14388,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
@@ -14423,7 +14423,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>1</v>
@@ -14629,7 +14629,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
@@ -14642,7 +14642,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>0</v>
@@ -15209,13 +15209,13 @@
         <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -619,7 +619,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -1459,7 +1459,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -2620,7 +2620,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -2782,7 +2782,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -3268,7 +3268,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -3595,7 +3595,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -4096,7 +4096,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -6220,7 +6220,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6508,7 +6508,7 @@
                 <v>1</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6940,7 +6940,7 @@
                 <v>4</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -7084,7 +7084,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -7249,7 +7249,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -7984,7 +7984,7 @@
                 <v>1</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -8128,7 +8128,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -8560,7 +8560,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -8609,7 +8609,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8704,7 +8704,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -9028,7 +9028,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -10393,7 +10393,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -10903,10 +10903,10 @@
                 <v>2</v>
               </pt>
               <pt idx="2">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -10918,7 +10918,7 @@
                 <v>1</v>
               </pt>
               <pt idx="7">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="8">
                 <v>5</v>
@@ -11101,7 +11101,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -13294,7 +13294,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>0</v>
@@ -13396,10 +13396,10 @@
         <v>2</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>1</v>
@@ -13411,7 +13411,7 @@
         <v>1</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="4" t="n">
         <v>5</v>
@@ -13448,7 +13448,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -13610,7 +13610,7 @@
         <v>0</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="358.5826771653543" customHeight="1">
@@ -13750,7 +13750,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>0</v>
@@ -14089,7 +14089,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>1</v>
@@ -14142,7 +14142,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
@@ -14581,7 +14581,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>0</v>
@@ -14613,7 +14613,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>0</v>
@@ -14661,7 +14661,7 @@
         <v>4</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
@@ -14677,7 +14677,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>1</v>
@@ -14839,7 +14839,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>0</v>
@@ -14887,7 +14887,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>1</v>
@@ -14903,7 +14903,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0</v>
@@ -14919,7 +14919,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0</v>
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>0</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -259,7 +259,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -1795,7 +1795,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -4702,7 +4702,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -4757,7 +4757,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5002,7 +5002,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -7243,7 +7243,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -7255,7 +7255,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -13164,7 +13164,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
@@ -13300,7 +13300,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -13806,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>0</v>
@@ -14385,7 +14385,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>2</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -250,7 +250,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -610,7 +610,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -943,7 +943,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -1444,10 +1444,10 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -1780,10 +1780,10 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -2128,7 +2128,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -3604,10 +3604,10 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -6076,7 +6076,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -7252,7 +7252,7 @@
                 <v>1</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -7981,7 +7981,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -8413,7 +8413,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -8557,7 +8557,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -8872,7 +8872,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -10906,7 +10906,7 @@
                 <v>3</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -13155,7 +13155,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
@@ -13195,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="4" t="n">
         <v>0</v>
@@ -13297,7 +13297,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>1</v>
@@ -13331,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>0</v>
@@ -13399,7 +13399,7 @@
         <v>3</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>1</v>
@@ -13601,7 +13601,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>0</v>
@@ -13654,7 +13654,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="4" t="n">
         <v>0</v>
@@ -13735,10 +13735,10 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>0</v>
@@ -13791,10 +13791,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -14565,7 +14565,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>0</v>
@@ -14820,7 +14820,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>2</v>
@@ -14868,7 +14868,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
@@ -14884,7 +14884,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>2</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -262,7 +262,7 @@
                 <v>1</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="6">
                 <v>1</v>
@@ -442,7 +442,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="6">
                 <v>0</v>
@@ -4705,7 +4705,7 @@
                 <v>4</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -5002,7 +5002,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -5155,7 +5155,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -5455,7 +5455,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6367,7 +6367,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -6799,7 +6799,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -7087,7 +7087,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -7258,7 +7258,7 @@
                 <v>1</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="6">
                 <v>3</v>
@@ -7267,7 +7267,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -8878,7 +8878,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="6">
                 <v>2</v>
@@ -13167,7 +13167,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>1</v>
@@ -13303,7 +13303,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>3</v>
@@ -13312,7 +13312,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>2</v>
@@ -13473,7 +13473,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="4" t="n">
         <v>0</v>
@@ -14350,7 +14350,7 @@
         <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0</v>
@@ -14385,7 +14385,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>2</v>
@@ -14407,7 +14407,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0</v>
@@ -14445,7 +14445,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0</v>
@@ -14600,7 +14600,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -14648,7 +14648,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -14680,7 +14680,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -253,7 +253,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -610,7 +610,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -665,7 +665,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -1450,7 +1450,7 @@
                 <v>1</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -1780,7 +1780,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>2</v>
@@ -2632,7 +2632,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -2782,7 +2782,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -2956,7 +2956,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -4108,7 +4108,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -4255,7 +4255,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -5308,7 +5308,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -8869,7 +8869,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>1</v>
@@ -10900,10 +10900,10 @@
                 <v>2</v>
               </pt>
               <pt idx="1">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="2">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="3">
                 <v>2</v>
@@ -13158,7 +13158,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="4" t="n">
         <v>0</v>
@@ -13328,7 +13328,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>1</v>
@@ -13393,10 +13393,10 @@
         <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>2</v>
@@ -13601,7 +13601,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>2</v>
@@ -14001,7 +14001,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>0</v>
@@ -14051,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -14201,7 +14201,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
@@ -14429,7 +14429,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -610,7 +610,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -665,7 +665,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2464,7 +2464,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -3112,7 +3112,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -4708,7 +4708,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -4858,7 +4858,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -5308,7 +5308,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -5357,7 +5357,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5929,7 +5929,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -6361,7 +6361,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -6937,7 +6937,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8557,7 +8557,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -10252,7 +10252,7 @@
                 <v>2</v>
               </pt>
               <pt idx="4">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="5">
                 <v>1</v>
@@ -10906,7 +10906,7 @@
                 <v>4</v>
               </pt>
               <pt idx="3">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -10921,7 +10921,7 @@
                 <v>2</v>
               </pt>
               <pt idx="8">
-                <v>5</v>
+                <v>6</v>
               </pt>
             </numLit>
           </val>
@@ -10967,7 +10967,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="6"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -13399,7 +13399,7 @@
         <v>4</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>1</v>
@@ -13414,7 +13414,7 @@
         <v>2</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -13601,7 +13601,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="4" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>0</v>
@@ -14353,7 +14353,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>0</v>
@@ -14372,7 +14372,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>0</v>
@@ -14429,7 +14429,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>0</v>
@@ -14594,7 +14594,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>1</v>
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>1</v>
@@ -14884,7 +14884,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>2</v>
@@ -15212,7 +15212,7 @@
         <v>2</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>1</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -940,7 +940,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -1780,7 +1780,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="2">
                 <v>2</v>
@@ -1841,7 +1841,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2467,7 +2467,7 @@
                 <v>1</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -3277,7 +3277,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -4705,7 +4705,7 @@
                 <v>4</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -6364,7 +6364,7 @@
                 <v>2</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -6796,7 +6796,7 @@
                 <v>1</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -6940,7 +6940,7 @@
                 <v>5</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -10252,7 +10252,7 @@
                 <v>2</v>
               </pt>
               <pt idx="4">
-                <v>2</v>
+                <v>4</v>
               </pt>
               <pt idx="5">
                 <v>1</v>
@@ -10301,7 +10301,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -10903,7 +10903,7 @@
                 <v>3</v>
               </pt>
               <pt idx="2">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="3">
                 <v>3</v>
@@ -10921,7 +10921,7 @@
                 <v>2</v>
               </pt>
               <pt idx="8">
-                <v>6</v>
+                <v>8</v>
               </pt>
             </numLit>
           </val>
@@ -10967,7 +10967,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6"/>
+          <max val="8"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -13396,7 +13396,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>3</v>
@@ -13414,7 +13414,7 @@
         <v>2</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -13651,7 +13651,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>1</v>
@@ -13791,7 +13791,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>2</v>
@@ -13973,7 +13973,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>1</v>
@@ -14098,7 +14098,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>1</v>
@@ -14350,7 +14350,7 @@
         <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>1</v>
@@ -14597,7 +14597,7 @@
         <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>1</v>
@@ -14645,7 +14645,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>1</v>
@@ -14661,7 +14661,7 @@
         <v>5</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
@@ -15212,7 +15212,7 @@
         <v>2</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>1</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -445,7 +445,7 @@
                 <v>1</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="7">
                 <v>0</v>
@@ -1447,7 +1447,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>1</v>
@@ -1456,7 +1456,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="6">
                 <v>1</v>
@@ -1780,7 +1780,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="2">
                 <v>2</v>
@@ -1841,7 +1841,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2128,7 +2128,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -2626,7 +2626,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -2950,7 +2950,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -5008,7 +5008,7 @@
                 <v>2</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -5308,7 +5308,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -5357,7 +5357,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5626,7 +5626,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -5935,7 +5935,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -6361,7 +6361,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -6413,7 +6413,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6649,7 +6649,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -6937,10 +6937,10 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>5</v>
+                <v>7</v>
               </pt>
               <pt idx="1">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="7"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7087,7 +7087,7 @@
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -7252,7 +7252,7 @@
                 <v>1</v>
               </pt>
               <pt idx="3">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -8872,7 +8872,7 @@
                 <v>1</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -10903,7 +10903,7 @@
                 <v>3</v>
               </pt>
               <pt idx="2">
-                <v>5</v>
+                <v>6</v>
               </pt>
               <pt idx="3">
                 <v>3</v>
@@ -10921,7 +10921,7 @@
                 <v>2</v>
               </pt>
               <pt idx="8">
-                <v>8</v>
+                <v>9</v>
               </pt>
             </numLit>
           </val>
@@ -10967,7 +10967,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="8"/>
+          <max val="9"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -13195,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="4" t="n">
         <v>0</v>
@@ -13263,7 +13263,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>0</v>
@@ -13297,7 +13297,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>1</v>
@@ -13331,7 +13331,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>0</v>
@@ -13396,7 +13396,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>3</v>
@@ -13414,7 +13414,7 @@
         <v>2</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -13476,7 +13476,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>1</v>
@@ -13747,7 +13747,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>1</v>
@@ -13791,7 +13791,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>2</v>
@@ -13995,7 +13995,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -14045,7 +14045,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>0</v>
@@ -14391,7 +14391,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>0</v>
@@ -14429,7 +14429,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
@@ -14552,7 +14552,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="358.5826771653543" customHeight="1">
@@ -14594,7 +14594,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>2</v>
@@ -14626,7 +14626,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>1</v>
@@ -14658,10 +14658,10 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -604,7 +604,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -1780,7 +1780,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="2">
                 <v>2</v>
@@ -1841,7 +1841,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2458,7 +2458,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -2620,7 +2620,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -2944,7 +2944,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -3106,7 +3106,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -3268,13 +3268,13 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>1</v>
@@ -3601,7 +3601,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -6361,10 +6361,10 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
+                <v>4</v>
+              </pt>
+              <pt idx="1">
                 <v>3</v>
-              </pt>
-              <pt idx="1">
-                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -6413,7 +6413,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6649,7 +6649,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -6793,10 +6793,10 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -6845,7 +6845,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6937,10 +6937,10 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>7</v>
+                <v>8</v>
               </pt>
               <pt idx="1">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="7"/>
+          <max val="8"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7249,7 +7249,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>3</v>
@@ -8869,7 +8869,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>2</v>
@@ -10903,10 +10903,10 @@
                 <v>3</v>
               </pt>
               <pt idx="2">
-                <v>6</v>
+                <v>7</v>
               </pt>
               <pt idx="3">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -13294,7 +13294,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>3</v>
@@ -13328,7 +13328,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>2</v>
@@ -13396,10 +13396,10 @@
         <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>1</v>
@@ -13595,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>2</v>
@@ -13964,7 +13964,7 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>1</v>
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>0</v>
@@ -14064,7 +14064,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>1</v>
@@ -14089,13 +14089,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>1</v>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>1</v>
@@ -14594,10 +14594,10 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>1</v>
@@ -14626,7 +14626,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>1</v>
@@ -14642,10 +14642,10 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>1</v>
@@ -14658,10 +14658,10 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -1786,7 +1786,7 @@
                 <v>2</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -5161,7 +5161,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -5302,7 +5302,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>2</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -5311,7 +5311,7 @@
                 <v>4</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -5782,7 +5782,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -6649,7 +6649,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -6796,7 +6796,7 @@
                 <v>2</v>
               </pt>
               <pt idx="1">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -6845,7 +6845,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6937,10 +6937,10 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>8</v>
+                <v>9</v>
               </pt>
               <pt idx="1">
-                <v>4</v>
+                <v>6</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="8"/>
+          <max val="9"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7249,7 +7249,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>2</v>
+                <v>4</v>
               </pt>
               <pt idx="3">
                 <v>3</v>
@@ -7261,7 +7261,7 @@
                 <v>1</v>
               </pt>
               <pt idx="6">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="7">
                 <v>0</v>
@@ -10897,13 +10897,13 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>3</v>
               </pt>
               <pt idx="2">
-                <v>7</v>
+                <v>8</v>
               </pt>
               <pt idx="3">
                 <v>4</v>
@@ -13294,7 +13294,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>3</v>
@@ -13306,7 +13306,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P8" s="4" t="n">
         <v>0</v>
@@ -13390,13 +13390,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>4</v>
@@ -13797,7 +13797,7 @@
         <v>2</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>0</v>
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -14423,7 +14423,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>1</v>
@@ -14432,7 +14432,7 @@
         <v>4</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -14461,7 +14461,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0</v>
@@ -14626,7 +14626,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>1</v>
@@ -14645,7 +14645,7 @@
         <v>2</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>1</v>
@@ -14658,10 +14658,10 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -949,7 +949,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -1123,7 +1123,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -1459,7 +1459,7 @@
                 <v>1</v>
               </pt>
               <pt idx="6">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -1789,13 +1789,13 @@
                 <v>1</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -3601,7 +3601,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -5005,7 +5005,7 @@
                 <v>4</v>
               </pt>
               <pt idx="1">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -5302,7 +5302,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -5311,7 +5311,7 @@
                 <v>4</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -5357,7 +5357,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5626,7 +5626,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -7984,7 +7984,7 @@
                 <v>2</v>
               </pt>
               <pt idx="1">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -8033,7 +8033,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8272,7 +8272,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -8866,7 +8866,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>2</v>
@@ -13263,7 +13263,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>0</v>
@@ -13325,7 +13325,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>2</v>
@@ -13660,7 +13660,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
@@ -13694,7 +13694,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -13750,7 +13750,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -13800,13 +13800,13 @@
         <v>1</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>1</v>
@@ -14388,7 +14388,7 @@
         <v>4</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>1</v>
@@ -14423,7 +14423,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>1</v>
@@ -14432,7 +14432,7 @@
         <v>4</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -14823,7 +14823,7 @@
         <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>1</v>
@@ -14855,7 +14855,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>

--- a/重点商品CA別進捗_2026年10月.xlsx
+++ b/重点商品CA別進捗_2026年10月.xlsx
@@ -436,7 +436,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -604,7 +604,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -1441,7 +1441,7 @@
             <numLit>
               <ptCount val="7"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -1453,7 +1453,7 @@
                 <v>1</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>1</v>
@@ -1777,7 +1777,7 @@
             <numLit>
               <ptCount val="7"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>5</v>
@@ -1951,7 +1951,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -2128,7 +2128,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -2143,7 +2143,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -2189,7 +2189,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2461,7 +2461,7 @@
                 <v>1</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -2623,7 +2623,7 @@
                 <v>2</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -2947,7 +2947,7 @@
                 <v>2</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -3109,7 +3109,7 @@
                 <v>2</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -3268,13 +3268,13 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>3</v>
+                <v>5</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>1</v>
@@ -3949,7 +3949,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -5002,7 +5002,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="1">
                 <v>3</v>
@@ -5057,7 +5057,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5302,7 +5302,7 @@
             <numLit>
               <ptCount val="4"/>
               <pt idx="0">
-                <v>5</v>
+                <v>6</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -5311,7 +5311,7 @@
                 <v>4</v>
               </pt>
               <pt idx="3">
-                <v>2</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -5357,7 +5357,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="6"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5641,7 +5641,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -5785,7 +5785,7 @@
                 <v>1</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -5929,7 +5929,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -5981,7 +5981,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6361,10 +6361,10 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
+                <v>8</v>
+              </pt>
+              <pt idx="1">
                 <v>4</v>
-              </pt>
-              <pt idx="1">
-                <v>3</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -6413,7 +6413,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="8"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6505,7 +6505,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -6649,10 +6649,10 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>3</v>
+                <v>6</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6701,7 +6701,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="6"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6796,7 +6796,7 @@
                 <v>2</v>
               </pt>
               <pt idx="1">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -6845,7 +6845,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6937,10 +6937,10 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>9</v>
+                <v>11</v>
               </pt>
               <pt idx="1">
-                <v>6</v>
+                <v>7</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -6989,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="9"/>
+          <max val="11"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7243,7 +7243,7 @@
             <numLit>
               <ptCount val="9"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -7267,7 +7267,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>1</v>
+                <v>4</v>
               </pt>
             </numLit>
           </val>
@@ -7981,7 +7981,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>3</v>
@@ -8413,7 +8413,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -8465,7 +8465,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8557,7 +8557,7 @@
             <numLit>
               <ptCount val="3"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
@@ -8609,7 +8609,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8887,7 +8887,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -9322,7 +9322,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="1">
                 <v>0</v>
@@ -9487,7 +9487,7 @@
                 <v>0</v>
               </pt>
               <pt idx="4">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="5">
                 <v>0</v>
@@ -9787,7 +9787,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -9940,7 +9940,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -10252,7 +10252,7 @@
                 <v>2</v>
               </pt>
               <pt idx="4">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="5">
                 <v>1</v>
@@ -10301,7 +10301,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -10903,10 +10903,10 @@
                 <v>3</v>
               </pt>
               <pt idx="2">
-                <v>8</v>
+                <v>9</v>
               </pt>
               <pt idx="3">
-                <v>4</v>
+                <v>6</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -10921,7 +10921,7 @@
                 <v>2</v>
               </pt>
               <pt idx="8">
-                <v>9</v>
+                <v>13</v>
               </pt>
             </numLit>
           </val>
@@ -10967,7 +10967,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="9"/>
+          <max val="13"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -11086,7 +11086,7 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -13195,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="4" t="n">
         <v>0</v>
@@ -13210,7 +13210,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -13244,7 +13244,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -13278,7 +13278,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
@@ -13312,7 +13312,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -13346,7 +13346,7 @@
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -13396,10 +13396,10 @@
         <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>1</v>
@@ -13414,7 +13414,7 @@
         <v>2</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -13433,7 +13433,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="4" t="n">
         <v>1</v>
@@ -13467,7 +13467,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="4" t="n">
         <v>0</v>
@@ -13595,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
@@ -13732,7 +13732,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>1</v>
@@ -13744,7 +13744,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>1</v>
@@ -13788,7 +13788,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>5</v>
@@ -13822,7 +13822,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="4" t="n">
         <v>0</v>
@@ -13967,7 +13967,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>1</v>
@@ -13992,7 +13992,7 @@
         <v>2</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>1</v>
@@ -14042,7 +14042,7 @@
         <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>1</v>
@@ -14067,7 +14067,7 @@
         <v>2</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>1</v>
@@ -14089,13 +14089,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>1</v>
@@ -14385,7 +14385,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>3</v>
@@ -14423,7 +14423,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>1</v>
@@ -14432,7 +14432,7 @@
         <v>4</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -14464,7 +14464,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>0</v>
@@ -14594,10 +14594,10 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>1</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>1</v>
@@ -14626,10 +14626,10 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
@@ -14645,7 +14645,7 @@
         <v>2</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>1</v>
@@ -14658,10 +14658,10 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
@@ -14820,7 +14820,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>3</v>
@@ -14868,7 +14868,7 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
@@ -14884,7 +14884,7 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>2</v>
@@ -15050,7 +15050,7 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -15087,7 +15087,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
@@ -15131,7 +15131,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>0</v>
@@ -15156,7 +15156,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>0</v>
@@ -15212,7 +15212,7 @@
         <v>2</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>1</v>
